--- a/excel_files/8.5.2.1.xlsx
+++ b/excel_files/8.5.2.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A01CE0EB-BD2A-49DE-8298-2611932916F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист" sheetId="1" r:id="rId1"/>
@@ -73,28 +74,28 @@
     <t>Men</t>
   </si>
   <si>
-    <t>1.3.1.1е Уровень официально зарегистрированных безработных</t>
-  </si>
-  <si>
     <t>(в процентах)</t>
   </si>
   <si>
     <t>(пайыз менен)</t>
   </si>
   <si>
-    <t>1.3.1.1e Жумушсуз расмий катталгандардын дэңгээли</t>
+    <t>(in percent)</t>
   </si>
   <si>
-    <t>1.3.1.1e Share of officially registered unemployed</t>
+    <t>8.5.2.1 Жумушсуз расмий катталгандардын дэңгээли</t>
   </si>
   <si>
-    <t>(in percent)</t>
+    <t>8.5.2.1 Уровень официально зарегистрированных безработных</t>
+  </si>
+  <si>
+    <t>8.5.2.1 Share of officially registered unemployed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
@@ -183,7 +184,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -191,7 +192,7 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -213,7 +214,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -225,11 +226,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal 17" xfId="1"/>
+    <cellStyle name="Normal 17" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 7" xfId="2"/>
+    <cellStyle name="Обычный 7" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -245,7 +253,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Data"/>
@@ -7971,8 +7979,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U24"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="28.25" style="8" customWidth="1"/>
@@ -7980,15 +7988,15 @@
     <col min="21" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="7"/>
@@ -8004,15 +8012,15 @@
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
     </row>
-    <row r="2" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>14</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>17</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="7"/>
@@ -8028,7 +8036,7 @@
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
     </row>
-    <row r="3" spans="1:20" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -8045,8 +8053,9 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
+      <c r="U3" s="15"/>
     </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>3</v>
       </c>
@@ -8107,8 +8116,11 @@
       <c r="T4" s="10">
         <v>2023</v>
       </c>
+      <c r="U4" s="16">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -8169,8 +8181,11 @@
       <c r="T5" s="2">
         <v>2.5</v>
       </c>
+      <c r="U5" s="17">
+        <v>1.7777016492697491</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>7</v>
       </c>
@@ -8231,8 +8246,11 @@
       <c r="T6" s="3">
         <v>2.7</v>
       </c>
+      <c r="U6" s="18">
+        <v>2.0294265973410255</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>8</v>
       </c>
@@ -8293,8 +8311,11 @@
       <c r="T7" s="5">
         <v>2.2000000000000002</v>
       </c>
+      <c r="U7" s="19">
+        <v>1.6128033769589434</v>
+      </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -8312,7 +8333,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -8330,7 +8351,7 @@
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -8348,7 +8369,7 @@
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -8366,7 +8387,7 @@
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -8384,7 +8405,7 @@
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -8402,7 +8423,7 @@
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -8420,7 +8441,7 @@
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -8438,7 +8459,7 @@
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
